--- a/data/1.abstracting/26_03_01_deduplicated_processed.xlsx
+++ b/data/1.abstracting/26_03_01_deduplicated_processed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/1.abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{F173A33B-F0B2-419C-86F7-EB05A9A47363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{434CFB39-8E25-482B-9741-E0A6ECA6D7B7}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{F173A33B-F0B2-419C-86F7-EB05A9A47363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BD46F13-7614-4633-93B6-F5784E37F7B0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F07D3D19-D3EA-45BC-959B-92AE09358097}"/>
+    <workbookView xWindow="47235" yWindow="765" windowWidth="9600" windowHeight="9720" xr2:uid="{F07D3D19-D3EA-45BC-959B-92AE09358097}"/>
   </bookViews>
   <sheets>
     <sheet name="articles" sheetId="1" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>Policymakers recognize the importance of socio-emotional skills (SES) for workforce development. However, it is unclear if SES programming could be used to improve gender gaps in the labor force, and whether gender differences exist in these skills or returns to these skills. The answer may depend on how SES are measured. Few studies use measures beyond self-reports - or seek to measure SES granularly and rigorously in large samples, especially in low-and middle-income countries. This paper deploys novel sets of self-reported and behavioral measures of 14 SES in a sample of more than 4000 male and female youth not in full-time education, employment or training, in urban and peri-urban Tanzania. The findings show that the two measures are not highly correlated. Moreover, men score higher than women on all 12 positively-worded self-reported measures. In contrast, gender gaps in behavioral measures are only observed for a few skills, and are far smaller in magnitude. The paper provides suggestive correlational evidence that this pattern reflects men's overestimation of their own skills, rather than women's underestimation. In particular, there is a larger gap between self-reported and behavioral measures among men. Men's self-reports, and the gap between their self-reported and behavioral measures, are strongly correlated with measures of social desirability and gendered beliefs about abilities - patterns not observed among women.</t>
   </si>
   <si>
-    <t>10.1016/j.socec.2026.102530</t>
-  </si>
-  <si>
     <t>rayyan-477552171</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>Emotional risks are ubiquitous in social work practice and pose significant threats to the health and well-being of practitioners and clients. Emotional skills are recognized as the best practice approach for coping with these risks. However, existing research on emotional skills is almost all from the fields of medicine, education, and psychology, and little attention is paid to it in the social work literature. To address this gap, the study explored Chinese social workers' experiences and perceptions of using emotional skills in practice through semistructured interviews (N = 28). The study suggests that emotion can be used as a practical skill for social workers, who have developed two patterns of practice for emotional skills: ``self-directed{''} emotion management and ``other-directed{''} emotion management. In the practice of coping with emotional risk in oneself and others, social workers navigated three stages of identification, understanding, and management and employed relevant professional skills (such as body scanning, empathy, and communicating emotions to others). The study results are pragmatic, and the action plan model of emotional skills has significant implications for social work practice and education.</t>
   </si>
   <si>
-    <t>10.1093/sw/swag005</t>
-  </si>
-  <si>
     <t>rayyan-477552173</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>Many individuals likely struggle with patience on a daily or even hourly basis, but the empirical study of patience as a personality trait is still emerging. Recent theoretical work articulates patience as a trait (i.e., as a tendency to react in a particular way in particular context) and differentiates it from the regulation of patience (i.e., as one pathway toward patient reactions). We present the Patient Reaction (P-React) scale and the Patience Regulation (P-Reg) scale to address conceptual and practical limitations of existing assessments related to those constructs. Across 11 samples with nearly 2,000 unique participants (including student and non-student participants), we found that both scales had strong psychometric properties and produced validity correlations that corresponded strongly with a priori hypotheses based on the recent theoretical accounts of the constructs. Two forms of each scale were developed and are essentially psychometrically identical, facilitating their complementary use and their use in repeated-assessment contexts. We believe that the new scales will help advance research regarding important and commonly experienced constructs that have been surprisingly understudied to date.</t>
   </si>
   <si>
-    <t>10.1080/00223891.2026.2621759</t>
-  </si>
-  <si>
     <t>rayyan-477552177</t>
   </si>
   <si>
@@ -164,9 +155,6 @@
     <t>Pinheiro, Elaine Alves and Fonseca, Susana and Fonseca-Pinto, R. M. and Pinheiro, Rafael Fernandes</t>
   </si>
   <si>
-    <t>10.1109/INDUSCON66435.2025.11241398</t>
-  </si>
-  <si>
     <t>decision</t>
   </si>
   <si>
@@ -174,13 +162,25 @@
   </si>
   <si>
     <t>exclude</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.socec.2026.102530</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/sw/swag005</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/00223891.2026.2621759</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/INDUSCON66435.2025.11241398</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +311,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -613,7 +621,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -656,11 +664,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Colore 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Colore 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -682,6 +692,7 @@
     <cellStyle name="Calcolo" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Cella collegata" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Cella da controllare" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Collegamento ipertestuale" xfId="42" builtinId="8"/>
     <cellStyle name="Colore 1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Colore 2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Colore 3" xfId="26" builtinId="37" customBuiltin="1"/>
@@ -1066,15 +1077,15 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D2">
         <v>2026</v>
@@ -1092,148 +1103,154 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
         <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{9847139A-8613-48F3-9D67-6A8FE8D06BCC}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{3DD2032C-7322-4301-ADE0-F838901D21AD}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{FF2CDDD1-3E45-4CC1-B317-0D4D2773062B}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{8EE393CE-F6BB-4D83-9961-B97CB96D6694}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/1.abstracting/26_03_01_deduplicated_processed.xlsx
+++ b/data/1.abstracting/26_03_01_deduplicated_processed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/1.abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{F173A33B-F0B2-419C-86F7-EB05A9A47363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BD46F13-7614-4633-93B6-F5784E37F7B0}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{F173A33B-F0B2-419C-86F7-EB05A9A47363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A90FB8-D772-4EB0-928A-CDFCD51D09AD}"/>
   <bookViews>
-    <workbookView xWindow="47235" yWindow="765" windowWidth="9600" windowHeight="9720" xr2:uid="{F07D3D19-D3EA-45BC-959B-92AE09358097}"/>
+    <workbookView minimized="1" xWindow="30450" yWindow="1650" windowWidth="21600" windowHeight="11175" xr2:uid="{F07D3D19-D3EA-45BC-959B-92AE09358097}"/>
   </bookViews>
   <sheets>
     <sheet name="articles" sheetId="1" r:id="rId1"/>
